--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158903</v>
+        <v>123158902</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>56448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453046</v>
+        <v>453101</v>
       </c>
       <c r="R2" t="n">
-        <v>6487423</v>
+        <v>6487747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158902</v>
+        <v>123158903</v>
       </c>
       <c r="B3" t="n">
-        <v>56448</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100088</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453101</v>
+        <v>453046</v>
       </c>
       <c r="R3" t="n">
-        <v>6487747</v>
+        <v>6487423</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158902</v>
+        <v>123158903</v>
       </c>
       <c r="B2" t="n">
-        <v>56448</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100088</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453101</v>
+        <v>453046</v>
       </c>
       <c r="R2" t="n">
-        <v>6487747</v>
+        <v>6487423</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158903</v>
+        <v>123158902</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>56448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453046</v>
+        <v>453101</v>
       </c>
       <c r="R3" t="n">
-        <v>6487423</v>
+        <v>6487747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123158903</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123158902</v>
       </c>
       <c r="B3" t="n">
-        <v>56448</v>
+        <v>56451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158903</v>
+        <v>123158902</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>56451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453046</v>
+        <v>453101</v>
       </c>
       <c r="R2" t="n">
-        <v>6487423</v>
+        <v>6487747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158902</v>
+        <v>123158903</v>
       </c>
       <c r="B3" t="n">
-        <v>56451</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100088</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453101</v>
+        <v>453046</v>
       </c>
       <c r="R3" t="n">
-        <v>6487747</v>
+        <v>6487423</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158902</v>
+        <v>123158903</v>
       </c>
       <c r="B2" t="n">
-        <v>56451</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100088</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453101</v>
+        <v>453046</v>
       </c>
       <c r="R2" t="n">
-        <v>6487747</v>
+        <v>6487423</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158903</v>
+        <v>123158902</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>56457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453046</v>
+        <v>453101</v>
       </c>
       <c r="R3" t="n">
-        <v>6487423</v>
+        <v>6487747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158903</v>
+        <v>123158902</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>56460</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453046</v>
+        <v>453101</v>
       </c>
       <c r="R2" t="n">
-        <v>6487423</v>
+        <v>6487747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158902</v>
+        <v>123158903</v>
       </c>
       <c r="B3" t="n">
-        <v>56457</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100088</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453101</v>
+        <v>453046</v>
       </c>
       <c r="R3" t="n">
-        <v>6487747</v>
+        <v>6487423</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123158903</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 61281-2023 artfynd.xlsx
+++ b/artfynd/A 61281-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123158902</v>
       </c>
       <c r="B2" t="n">
-        <v>56460</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>123158903</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
